--- a/NO_CONN_001/Deliverables/NO_CONN_001_values.xlsx
+++ b/NO_CONN_001/Deliverables/NO_CONN_001_values.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>area</t>
   </si>
@@ -134,10 +134,22 @@
     <t>EPSG:25833 (ETRS89 / UTM 33N)</t>
   </si>
   <si>
+    <t>Variant</t>
+  </si>
+  <si>
+    <t>AR5 variant. The alternative mire-model variant (national mire probability model + NiN in the north) is documented in Data/connectivity_scored/README_variants.md. The two are NOT on a common scale: the anchors are percentiles of each run's own distribution. A side-check separating the two effects shows the anchor change is small and uniform (-0.017 to -0.034 per region) while the population change dominates (+0.233 in Nord-Norge, -0.03 to -0.10 elsewhere)</t>
+  </si>
+  <si>
+    <t>Wetland population</t>
+  </si>
+  <si>
+    <t>AR5 (national land-resource map, ARTYPE 60 myr), adjacent polygons dissolved into connected patches</t>
+  </si>
+  <si>
     <t>Data year label</t>
   </si>
   <si>
-    <t>2023: N50 infrastructure and land-use-intensity layers of 2023; mire polygons from the national mire probability model (MyrMod2Rv, simplified) and NiN</t>
+    <t>2023: N50 infrastructure and land-use-intensity layers of 2023; wetland polygons from AR5 (NIBIO)</t>
   </si>
   <si>
     <t>Variable (v)</t>
@@ -155,19 +167,19 @@
     <t>Scaling function</t>
   </si>
   <si>
-    <t>Linear on log(kvotient), truncated; no sigmoid. Percentile anchors (1st / 99th) computed from the national run itself (n = 97,072 finite non-zero values), following the aggregation framework of Kolstad et al. (in prep). The original indicator never finalised a scaling function (ecosystemCondition issue #144); this is our reconstruction</t>
+    <t>Linear on log(kvotient), truncated; no sigmoid. Percentile anchors (1st / 99th) computed from this run itself (n = 111,397 finite non-zero values), following the aggregation framework of Kolstad et al. (in prep). The original indicator never finalised a scaling function (ecosystemCondition issue #144); this is our reconstruction</t>
   </si>
   <si>
     <t>reference_high (X100)</t>
   </si>
   <si>
-    <t>kvotient = 177.75 (99th percentile of log kvotient): infrastructure ~178x farther than the nearest mire</t>
+    <t>kvotient = 1487.66 (99th percentile of log kvotient): infrastructure about 1488x farther away than the nearest other mire</t>
   </si>
   <si>
     <t>reference_low (X0)</t>
   </si>
   <si>
-    <t>kvotient = 0.1414 (1st percentile): infrastructure ~7x closer than the nearest mire</t>
+    <t>kvotient = 0.1562 (1st percentile): infrastructure about 6x closer than the nearest other mire</t>
   </si>
   <si>
     <t>Threshold (thr)</t>
@@ -185,13 +197,13 @@
     <t>Number of observations</t>
   </si>
   <si>
-    <t>1151903 mire polygons with an index value (97076 scaled, 1038752 reference-anchored, 16075 zero-anchored); total mire area 7769 km2</t>
+    <t>720460 mire polygons with an index value (111403 scaled, 583934 reference-anchored, 25123 zero-anchored); total mire area 13896 km2</t>
   </si>
   <si>
     <t>Coverage caveat</t>
   </si>
   <si>
-    <t>The national mire probability map (MyrMod2Rv) covers Norway only to ~64 N. South of that, mire polygons come from the map + NiN; Nord-Norge is NiN-mapped mires ONLY (4,917 polygons, sparse, 48.6 % with infrastructure within 1000 m) and Midt-Norge is partially covered. Nord-Norge's value (0.65) therefore describes a different, much smaller and more human-proximate polygon population than the other regions' (0.96-0.98) and is not comparable to them; the national row is dominated by the four southern regions</t>
+    <t>AR5 covers the whole country, so all five regions describe a comparable wetland population - including Nord-Norge (127,464 polygons here against 4,917 in the mire-model variant, which had no data north of ~64 N). AR5 also includes lowland and farm-edge wetland the mire-probability model never mapped, so the share of wetland within 1000 m of infrastructure is roughly twice as high outside the north and the index is correspondingly lower. Note that AR5 is not publicly downloadable; the fully open AR50 is the fallback for users without access</t>
   </si>
   <si>
     <t>Justification of references</t>
@@ -203,13 +215,13 @@
     <t>Data sources</t>
   </si>
   <si>
-    <t>Kartverket N50 (open); Miljødirektoratet mire probability model MyrMod2Rv; NiN nature types (open); NVE regulated lakes (open); regions.shp</t>
+    <t>Kartverket N50 (open); AR5 land-resource map, NIBIO (access-restricted - see the access caveat); NVE regulated lakes (open); regions.shp</t>
   </si>
   <si>
     <t>Method note</t>
   </si>
   <si>
-    <t>Reconstruction of NINA's connectivity indicator (Bakkestuen; GEE workflow not public). Distance computations reproduced in R on the certified nearest-neighbour algorithm; scaling and regional aggregation are ours (see Scaling function)</t>
+    <t>Reconstruction of NINA's connectivity indicator (Bakkestuen). The original Earth Engine code is embedded in the published indicator documentation and was followed line by line; its two private data assets (mire probability model, infrastructure index) were rebuilt from open sources. This variant additionally replaces the mire population with AR5, which is a deliberate deviation from the original, made to obtain national coverage. Scaling and regional aggregation are ours (see Scaling function)</t>
   </si>
   <si>
     <t>Documentation</t>
@@ -233,7 +245,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-16 15:45</t>
+    <t>2026-09-22 16:37</t>
   </si>
 </sst>
 </file>
@@ -634,43 +646,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>10.2125978693586</v>
+        <v>31.30802457115686</v>
       </c>
       <c r="D2">
-        <v>0.0362613057583247</v>
+        <v>0.009251390224014108</v>
       </c>
       <c r="E2">
-        <v>0.6477198202502086</v>
+        <v>0.8554261813247079</v>
       </c>
       <c r="F2">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G2">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H2">
         <v>0.6</v>
       </c>
       <c r="I2">
-        <v>4917</v>
+        <v>127464</v>
       </c>
       <c r="J2">
-        <v>1748</v>
+        <v>20064</v>
       </c>
       <c r="K2">
-        <v>2524</v>
+        <v>102302</v>
       </c>
       <c r="L2">
-        <v>645</v>
+        <v>5098</v>
       </c>
       <c r="M2">
-        <v>0.573700126071173</v>
+        <v>0.836725169072487</v>
       </c>
       <c r="N2">
-        <v>0.714606047617972</v>
+        <v>0.872460243543059</v>
       </c>
       <c r="O2">
-        <v>88.07992142184857</v>
+        <v>2608.418078237027</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -681,43 +693,43 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>26.78894898954036</v>
+        <v>57.34425824661109</v>
       </c>
       <c r="D3">
-        <v>0.001401256047338885</v>
+        <v>0.003497393247259163</v>
       </c>
       <c r="E3">
-        <v>0.974348443505501</v>
+        <v>0.9113723044943653</v>
       </c>
       <c r="F3">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G3">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H3">
         <v>0.6</v>
       </c>
       <c r="I3">
-        <v>200934</v>
+        <v>186159</v>
       </c>
       <c r="J3">
-        <v>17205</v>
+        <v>26735</v>
       </c>
       <c r="K3">
-        <v>181540</v>
+        <v>154372</v>
       </c>
       <c r="L3">
-        <v>2189</v>
+        <v>5052</v>
       </c>
       <c r="M3">
-        <v>0.971519958759711</v>
+        <v>0.904568247499806</v>
       </c>
       <c r="N3">
-        <v>0.976926594157395</v>
+        <v>0.917953410397367</v>
       </c>
       <c r="O3">
-        <v>1590.665364711673</v>
+        <v>4616.112727434686</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -728,43 +740,43 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>22.42795484134464</v>
+        <v>43.40772880499643</v>
       </c>
       <c r="D4">
-        <v>0.0009520609448866888</v>
+        <v>0.002855225237840782</v>
       </c>
       <c r="E4">
-        <v>0.9708457076956668</v>
+        <v>0.916805687645624</v>
       </c>
       <c r="F4">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G4">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H4">
         <v>0.6</v>
       </c>
       <c r="I4">
-        <v>446468</v>
+        <v>203211</v>
       </c>
       <c r="J4">
-        <v>40017</v>
+        <v>27100</v>
       </c>
       <c r="K4">
-        <v>398871</v>
+        <v>170216</v>
       </c>
       <c r="L4">
-        <v>7580</v>
+        <v>5895</v>
       </c>
       <c r="M4">
-        <v>0.968933596935832</v>
+        <v>0.911305047091447</v>
       </c>
       <c r="N4">
-        <v>0.972591173930534</v>
+        <v>0.92198505139736</v>
       </c>
       <c r="O4">
-        <v>4152.860200000023</v>
+        <v>4681.944110705336</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -775,43 +787,43 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>21.21541825203401</v>
+        <v>28.44031403190902</v>
       </c>
       <c r="D5">
-        <v>0.001544760724901224</v>
+        <v>0.003316906394126562</v>
       </c>
       <c r="E5">
-        <v>0.9580119875214647</v>
+        <v>0.8251276597646489</v>
       </c>
       <c r="F5">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G5">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H5">
         <v>0.6</v>
       </c>
       <c r="I5">
-        <v>221250</v>
+        <v>78023</v>
       </c>
       <c r="J5">
-        <v>22178</v>
+        <v>19530</v>
       </c>
       <c r="K5">
-        <v>195485</v>
+        <v>52970</v>
       </c>
       <c r="L5">
-        <v>3587</v>
+        <v>5523</v>
       </c>
       <c r="M5">
-        <v>0.9549311789505091</v>
+        <v>0.8182219180144999</v>
       </c>
       <c r="N5">
-        <v>0.960998023768345</v>
+        <v>0.831237083319054</v>
       </c>
       <c r="O5">
-        <v>779.5165999999995</v>
+        <v>771.0736114269447</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -822,43 +834,43 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>18.18763306115341</v>
+        <v>26.78457711595037</v>
       </c>
       <c r="D6">
-        <v>0.0009212643172021457</v>
+        <v>0.01344305644527366</v>
       </c>
       <c r="E6">
-        <v>0.9761596384319782</v>
+        <v>0.9079651162948932</v>
       </c>
       <c r="F6">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G6">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H6">
         <v>0.6</v>
       </c>
       <c r="I6">
-        <v>278334</v>
+        <v>125603</v>
       </c>
       <c r="J6">
-        <v>15928</v>
+        <v>17974</v>
       </c>
       <c r="K6">
-        <v>260332</v>
+        <v>104074</v>
       </c>
       <c r="L6">
-        <v>2074</v>
+        <v>3555</v>
       </c>
       <c r="M6">
-        <v>0.974308740311956</v>
+        <v>0.87900007537154</v>
       </c>
       <c r="N6">
-        <v>0.977996271808336</v>
+        <v>0.923417938460939</v>
       </c>
       <c r="O6">
-        <v>1158.071399999998</v>
+        <v>1218.302243812976</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -869,43 +881,43 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>21.50619266270642</v>
+        <v>41.29512723864089</v>
       </c>
       <c r="D7">
-        <v>0.0008804274042095551</v>
+        <v>0.002601271940934337</v>
       </c>
       <c r="E7">
-        <v>0.9674039850770849</v>
+        <v>0.8976168287998739</v>
       </c>
       <c r="F7">
-        <v>177.746429147488</v>
+        <v>1487.66289053523</v>
       </c>
       <c r="G7">
-        <v>0.141392498501815</v>
+        <v>0.156176982580064</v>
       </c>
       <c r="H7">
         <v>0.6</v>
       </c>
       <c r="I7">
-        <v>1151903</v>
+        <v>720460</v>
       </c>
       <c r="J7">
-        <v>97076</v>
+        <v>111403</v>
       </c>
       <c r="K7">
-        <v>1038752</v>
+        <v>583934</v>
       </c>
       <c r="L7">
-        <v>16075</v>
+        <v>25123</v>
       </c>
       <c r="M7">
-        <v>0.9655945985709355</v>
+        <v>0.8925604700307628</v>
       </c>
       <c r="N7">
-        <v>0.9691737363306102</v>
+        <v>0.9021438542760409</v>
       </c>
       <c r="O7">
-        <v>7769.193486133542</v>
+        <v>13895.85077161697</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -1126,6 +1138,22 @@
         <v>72</v>
       </c>
     </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
